--- a/doc/Plan.xlsx
+++ b/doc/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyData\校内课程\大三\104 Agile Software Engineering\HappyASPA\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4160732B-60BD-422E-94DD-A7C6AD2D87C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45E3688-8C34-4D37-B583-D28BF5FF112F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5FB1177C-0C5A-4051-B37B-4695C3C6DFA5}"/>
   </bookViews>
@@ -241,7 +241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,22 +418,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
@@ -921,12 +906,6 @@
     <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -936,13 +915,19 @@
     <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1321,9 +1306,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EAAEDE9-BB80-4510-B8DA-B2280A44B885}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="26.5546875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="20.109375" defaultRowHeight="85.8" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="20.109375" style="8"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.6" customHeight="1">
+    <row r="1" spans="1:7" ht="32.4" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>69</v>
       </c>
@@ -1334,7 +1322,7 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1">
+    <row r="2" spans="1:7" ht="85.8" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1357,207 +1345,207 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66.45" customHeight="1">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:7" ht="80.400000000000006" customHeight="1">
+      <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="71.400000000000006" customHeight="1">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:7" ht="98.4" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="60.6" customHeight="1">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:7" ht="85.8" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="85.2" customHeight="1">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:7" ht="94.8" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="66.45" customHeight="1">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:7" ht="76.2" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="6" t="s">
         <v>39</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="71.400000000000006" customHeight="1">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:7" ht="97.8" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="58.8" customHeight="1">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:7" ht="69" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="64.8" customHeight="1">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:7" ht="78.599999999999994" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="76.2" customHeight="1">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:7" ht="112.2" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>67</v>
       </c>
       <c r="G11" s="1" t="s">
